--- a/Palmares/fichier excel/aggregats_ecoles_KASAI_CENTRAL12022.xlsx
+++ b/Palmares/fichier excel/aggregats_ecoles_KASAI_CENTRAL12022.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Famille\OneDrive\Documents\GitHub\Projet-tutore\Palmares\fichier excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6420ee82958214d8/Documents/GitHub/Projet-tutore/Palmares/fichier excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7790714-10A3-439C-A2D2-EB985D85475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Écoles" sheetId="1" r:id="rId1"/>
